--- a/scripts/DoAn4_Bemori/test/cases/SCR_DatHangNhanh.xlsx
+++ b/scripts/DoAn4_Bemori/test/cases/SCR_DatHangNhanh.xlsx
@@ -700,7 +700,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="40" customWidth="1" min="4" max="4"/>
   </cols>
@@ -801,7 +801,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>VERIFY_TEXT_CONTAINS</t>
+          <t>VERIFY_ELEMENT_TEXT_EQUALS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
